--- a/artfynd/A 41018-2025 artfynd.xlsx
+++ b/artfynd/A 41018-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>76303219</v>
+        <v>76303215</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628570.8504634576</v>
+        <v>628457</v>
       </c>
       <c r="R2" t="n">
-        <v>7113423.05779468</v>
+        <v>7113167</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2018-08-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-08-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>76303217</v>
+        <v>76303219</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628457.1053057777</v>
+        <v>628571</v>
       </c>
       <c r="R3" t="n">
-        <v>7113166.8526657</v>
+        <v>7113423</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2018-08-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-08-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,122 +870,6 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>76303218</v>
-      </c>
-      <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Högtjärnkullen, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>628570.8504634576</v>
-      </c>
-      <c r="R4" t="n">
-        <v>7113423.05779468</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2018-08-09</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2018-08-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 41018-2025 artfynd.xlsx
+++ b/artfynd/A 41018-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>76303215</v>
+        <v>135446336</v>
       </c>
       <c r="B2" t="n">
-        <v>91909</v>
+        <v>81355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Högtjärnkullen, Ås lm</t>
+          <t>Högtjärnskullen, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628457</v>
+        <v>628649</v>
       </c>
       <c r="R2" t="n">
-        <v>7113167</v>
+        <v>7113342</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-08-09</t>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-08-09</t>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,23 +770,23 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>76303219</v>
+        <v>76303215</v>
       </c>
       <c r="B3" t="n">
         <v>91909</v>
@@ -811,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628571</v>
+        <v>628457</v>
       </c>
       <c r="R3" t="n">
-        <v>7113423</v>
+        <v>7113167</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,6 +882,2768 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>76303219</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Högtjärnkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>628571</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7113423</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2018-08-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2018-08-09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135446327</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91937</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>628941</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7113295</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135446341</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91937</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>628536</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7113275</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135446324</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>628940</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7113354</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135446325</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>628926</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7113344</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135446333</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>628839</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7113318</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135446343</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>628502</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7113246</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135446339</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80500</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>628591</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7113329</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135446322</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>628946</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7113383</v>
+      </c>
+      <c r="S12" t="n">
+        <v>14</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135446328</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>628952</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7113280</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135446329</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>628941</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7113260</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135446331</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>628935</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7113289</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135446337</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>628646</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7113324</v>
+      </c>
+      <c r="S16" t="n">
+        <v>7</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135446344</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>628464</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7113163</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135446346</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>628826</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7113378</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135446347</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>628901</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7113403</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135446330</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>628938</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7113259</v>
+      </c>
+      <c r="S20" t="n">
+        <v>8</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135446345</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>628546</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7113306</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>varningsläte</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135446332</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>628916</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7113290</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>39 blomstänger</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135446340</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>628568</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7113311</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135446342</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>628511</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7113258</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>20 st</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135446334</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>628809</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7113315</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135446335</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>628761</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7113307</v>
+      </c>
+      <c r="S26" t="n">
+        <v>11</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135446338</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>628631</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7113332</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 41018-2025 artfynd.xlsx
+++ b/artfynd/A 41018-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446336</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76303215</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76303219</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446327</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446341</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1318,6 +1348,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446324</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1429,6 +1464,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446325</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1540,6 +1580,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446333</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1651,6 +1696,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446343</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1762,6 +1812,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446339</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1878,6 +1933,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446322</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1994,6 +2054,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446328</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2110,6 +2175,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446329</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2226,6 +2296,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446331</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2342,6 +2417,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446337</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2458,6 +2538,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446344</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2574,6 +2659,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446346</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2690,6 +2780,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446347</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2806,6 +2901,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446330</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2927,6 +3027,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446345</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3060,6 +3165,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446332</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3188,6 +3298,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446340</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3304,6 +3419,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446342</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3415,6 +3535,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446334</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3526,6 +3651,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446335</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3646,8 +3776,41 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446338</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 41018-2025 artfynd.xlsx
+++ b/artfynd/A 41018-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135446336</v>
       </c>
       <c r="B2" t="n">
-        <v>81355</v>
+        <v>81393</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>135446327</v>
       </c>
       <c r="B5" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>135446341</v>
       </c>
       <c r="B6" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135446324</v>
       </c>
       <c r="B7" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>135446325</v>
       </c>
       <c r="B8" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>135446333</v>
       </c>
       <c r="B9" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>135446343</v>
       </c>
       <c r="B10" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>135446339</v>
       </c>
       <c r="B11" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>135446322</v>
       </c>
       <c r="B12" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>135446328</v>
       </c>
       <c r="B13" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>135446329</v>
       </c>
       <c r="B14" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>135446331</v>
       </c>
       <c r="B15" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>135446337</v>
       </c>
       <c r="B16" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>135446344</v>
       </c>
       <c r="B17" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>135446346</v>
       </c>
       <c r="B18" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>135446347</v>
       </c>
       <c r="B19" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>135446330</v>
       </c>
       <c r="B20" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>135446345</v>
       </c>
       <c r="B21" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>135446332</v>
       </c>
       <c r="B22" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>135446340</v>
       </c>
       <c r="B23" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         <v>135446342</v>
       </c>
       <c r="B24" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>135446334</v>
       </c>
       <c r="B25" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>135446335</v>
       </c>
       <c r="B26" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>135446338</v>
       </c>
       <c r="B27" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 41018-2025 artfynd.xlsx
+++ b/artfynd/A 41018-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135446336</v>
       </c>
       <c r="B2" t="n">
-        <v>81393</v>
+        <v>81420</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>135446327</v>
       </c>
       <c r="B5" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>135446341</v>
       </c>
       <c r="B6" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135446324</v>
       </c>
       <c r="B7" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>135446325</v>
       </c>
       <c r="B8" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>135446333</v>
       </c>
       <c r="B9" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>135446343</v>
       </c>
       <c r="B10" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>135446339</v>
       </c>
       <c r="B11" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>135446332</v>
       </c>
       <c r="B22" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>135446340</v>
       </c>
       <c r="B23" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         <v>135446342</v>
       </c>
       <c r="B24" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>135446334</v>
       </c>
       <c r="B25" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>135446335</v>
       </c>
       <c r="B26" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>135446338</v>
       </c>
       <c r="B27" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 41018-2025 artfynd.xlsx
+++ b/artfynd/A 41018-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>76303215</v>
+        <v>135446336</v>
       </c>
       <c r="B2" t="n">
-        <v>91909</v>
+        <v>81423</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Högtjärnkullen, Ås lm</t>
+          <t>Högtjärnskullen, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628457</v>
+        <v>628649</v>
       </c>
       <c r="R2" t="n">
-        <v>7113167</v>
+        <v>7113342</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-08-09</t>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-08-09</t>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,28 +775,28 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/76303215</t>
+          <t>https://artportalen.se/Sighting/135446336</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>76303219</v>
+        <v>76303215</v>
       </c>
       <c r="B3" t="n">
         <v>91909</v>
@@ -821,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628571</v>
+        <v>628457</v>
       </c>
       <c r="R3" t="n">
-        <v>7113423</v>
+        <v>7113167</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,7 +896,2889 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/76303215</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>76303219</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Högtjärnkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>628571</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7113423</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2018-08-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2018-08-09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/76303219</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135446327</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92011</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>628941</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7113295</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446327</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135446341</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92011</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>628536</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7113275</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446341</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135446324</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>628940</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7113354</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446324</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135446325</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>628926</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7113344</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446325</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135446333</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>628839</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7113318</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446333</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135446343</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>628502</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7113246</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446343</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135446339</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80568</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>628591</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7113329</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446339</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135446322</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>628946</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7113383</v>
+      </c>
+      <c r="S12" t="n">
+        <v>14</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446322</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135446328</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>628952</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7113280</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446328</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135446329</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>628941</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7113260</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446329</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135446331</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>628935</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7113289</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446331</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135446337</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>628646</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7113324</v>
+      </c>
+      <c r="S16" t="n">
+        <v>7</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446337</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135446344</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>628464</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7113163</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446344</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135446346</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>628826</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7113378</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446346</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135446347</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>628901</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7113403</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446347</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135446330</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>628938</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7113259</v>
+      </c>
+      <c r="S20" t="n">
+        <v>8</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446330</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135446345</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>628546</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7113306</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>varningsläte</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446345</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135446332</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>628916</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7113290</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>39 blomstänger</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446332</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135446340</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>628568</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7113311</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446340</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135446342</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>628511</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7113258</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>20 st</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446342</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135446334</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99296</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>628809</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7113315</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446334</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135446335</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99296</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>628761</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7113307</v>
+      </c>
+      <c r="S26" t="n">
+        <v>11</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446335</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135446338</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99296</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Högtjärnskullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>628631</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7113332</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446338</t>
         </is>
       </c>
     </row>
@@ -894,6 +3786,30 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41018-2025 artfynd.xlsx
+++ b/artfynd/A 41018-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>135446327</v>
       </c>
       <c r="B5" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>135446341</v>
       </c>
       <c r="B6" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>135446332</v>
       </c>
       <c r="B22" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>135446340</v>
       </c>
       <c r="B23" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         <v>135446342</v>
       </c>
       <c r="B24" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>135446334</v>
       </c>
       <c r="B25" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>135446335</v>
       </c>
       <c r="B26" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>135446338</v>
       </c>
       <c r="B27" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 41018-2025 artfynd.xlsx
+++ b/artfynd/A 41018-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135446336</v>
       </c>
       <c r="B2" t="n">
-        <v>81423</v>
+        <v>81425</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>135446327</v>
       </c>
       <c r="B5" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>135446341</v>
       </c>
       <c r="B6" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135446324</v>
       </c>
       <c r="B7" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>135446325</v>
       </c>
       <c r="B8" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>135446333</v>
       </c>
       <c r="B9" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>135446343</v>
       </c>
       <c r="B10" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>135446339</v>
       </c>
       <c r="B11" t="n">
-        <v>80568</v>
+        <v>80570</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>135446322</v>
       </c>
       <c r="B12" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>135446328</v>
       </c>
       <c r="B13" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>135446329</v>
       </c>
       <c r="B14" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>135446331</v>
       </c>
       <c r="B15" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>135446337</v>
       </c>
       <c r="B16" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>135446344</v>
       </c>
       <c r="B17" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>135446346</v>
       </c>
       <c r="B18" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>135446347</v>
       </c>
       <c r="B19" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>135446330</v>
       </c>
       <c r="B20" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>135446345</v>
       </c>
       <c r="B21" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>135446332</v>
       </c>
       <c r="B22" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>135446340</v>
       </c>
       <c r="B23" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         <v>135446342</v>
       </c>
       <c r="B24" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>135446334</v>
       </c>
       <c r="B25" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>135446335</v>
       </c>
       <c r="B26" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>135446338</v>
       </c>
       <c r="B27" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
